--- a/artfynd/A 38327-2024 artfynd.xlsx
+++ b/artfynd/A 38327-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1170,6 +1170,732 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123299547</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90972</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stenbithålsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>615560</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6972753</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-06-14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-06-14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erik Lagerin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123299534</v>
+      </c>
+      <c r="B7" t="n">
+        <v>90970</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stenbithålsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>615549</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6972986</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-06-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-06-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erik Lagerin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123299521</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79847</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stenbithålsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>615350</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6972780</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>423</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-06-14</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-06-14</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erik Lagerin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123299533</v>
+      </c>
+      <c r="B9" t="n">
+        <v>90966</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stenbithålsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>615530</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6972995</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-06-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-06-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erik Lagerin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123299543</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stenbithålsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>615509</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6972912</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-06-14</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-06-14</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erik Lagerin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123299550</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91397</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stenbithålsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>615477</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6972749</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-06-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-06-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 38327-2024 artfynd.xlsx
+++ b/artfynd/A 38327-2024 artfynd.xlsx
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123299547</v>
+        <v>123299550</v>
       </c>
       <c r="B6" t="n">
-        <v>90972</v>
+        <v>91400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1187,25 +1187,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>615560</v>
+        <v>615477</v>
       </c>
       <c r="R6" t="n">
-        <v>6972753</v>
+        <v>6972749</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>393</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erik Lagerin</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1296,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123299534</v>
+        <v>123299521</v>
       </c>
       <c r="B7" t="n">
-        <v>90970</v>
+        <v>79850</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,21 +1312,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>615549</v>
+        <v>615350</v>
       </c>
       <c r="R7" t="n">
-        <v>6972986</v>
+        <v>6972780</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>423</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123299521</v>
+        <v>123299534</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>90973</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>615350</v>
+        <v>615549</v>
       </c>
       <c r="R8" t="n">
-        <v>6972780</v>
+        <v>6972986</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>410</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1541,7 +1541,7 @@
         <v>123299533</v>
       </c>
       <c r="B9" t="n">
-        <v>90966</v>
+        <v>90969</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1659,10 +1659,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123299543</v>
+        <v>123299547</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>90975</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1675,21 +1675,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>615509</v>
+        <v>615560</v>
       </c>
       <c r="R10" t="n">
-        <v>6972912</v>
+        <v>6972753</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>396</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1780,10 +1780,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123299550</v>
+        <v>123299543</v>
       </c>
       <c r="B11" t="n">
-        <v>91397</v>
+        <v>57481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1792,25 +1792,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1820,10 +1820,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>615477</v>
+        <v>615509</v>
       </c>
       <c r="R11" t="n">
-        <v>6972749</v>
+        <v>6972912</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>400</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Erik Lagerin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">

--- a/artfynd/A 38327-2024 artfynd.xlsx
+++ b/artfynd/A 38327-2024 artfynd.xlsx
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123299550</v>
+        <v>123299547</v>
       </c>
       <c r="B6" t="n">
-        <v>91400</v>
+        <v>90977</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1187,25 +1187,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>615477</v>
+        <v>615560</v>
       </c>
       <c r="R6" t="n">
-        <v>6972749</v>
+        <v>6972753</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>396</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Erik Lagerin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1299,7 +1299,7 @@
         <v>123299521</v>
       </c>
       <c r="B7" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123299534</v>
+        <v>123299533</v>
       </c>
       <c r="B8" t="n">
-        <v>90973</v>
+        <v>90971</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>615549</v>
+        <v>615530</v>
       </c>
       <c r="R8" t="n">
-        <v>6972986</v>
+        <v>6972995</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>411</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1538,10 +1538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123299533</v>
+        <v>123299534</v>
       </c>
       <c r="B9" t="n">
-        <v>90969</v>
+        <v>90975</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1554,21 +1554,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>615530</v>
+        <v>615549</v>
       </c>
       <c r="R9" t="n">
-        <v>6972995</v>
+        <v>6972986</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>410</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1659,10 +1659,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123299547</v>
+        <v>123299543</v>
       </c>
       <c r="B10" t="n">
-        <v>90975</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1675,21 +1675,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>615560</v>
+        <v>615509</v>
       </c>
       <c r="R10" t="n">
-        <v>6972753</v>
+        <v>6972912</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>400</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1780,10 +1780,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123299543</v>
+        <v>123299550</v>
       </c>
       <c r="B11" t="n">
-        <v>57481</v>
+        <v>91402</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1792,25 +1792,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1820,10 +1820,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>615509</v>
+        <v>615477</v>
       </c>
       <c r="R11" t="n">
-        <v>6972912</v>
+        <v>6972749</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>393</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erik Lagerin</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">

--- a/artfynd/A 38327-2024 artfynd.xlsx
+++ b/artfynd/A 38327-2024 artfynd.xlsx
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123299547</v>
+        <v>123299543</v>
       </c>
       <c r="B6" t="n">
-        <v>90977</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>615560</v>
+        <v>615509</v>
       </c>
       <c r="R6" t="n">
-        <v>6972753</v>
+        <v>6972912</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>400</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123299521</v>
+        <v>123299534</v>
       </c>
       <c r="B7" t="n">
-        <v>79852</v>
+        <v>90981</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,21 +1312,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>615350</v>
+        <v>615549</v>
       </c>
       <c r="R7" t="n">
-        <v>6972780</v>
+        <v>6972986</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>410</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123299533</v>
+        <v>123299550</v>
       </c>
       <c r="B8" t="n">
-        <v>90971</v>
+        <v>91408</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>615530</v>
+        <v>615477</v>
       </c>
       <c r="R8" t="n">
-        <v>6972995</v>
+        <v>6972749</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>393</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erik Lagerin</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1538,10 +1538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123299534</v>
+        <v>123299521</v>
       </c>
       <c r="B9" t="n">
-        <v>90975</v>
+        <v>79853</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1554,21 +1554,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>615549</v>
+        <v>615350</v>
       </c>
       <c r="R9" t="n">
-        <v>6972986</v>
+        <v>6972780</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>423</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1659,10 +1659,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123299543</v>
+        <v>123299547</v>
       </c>
       <c r="B10" t="n">
-        <v>57481</v>
+        <v>90983</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1675,21 +1675,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>615509</v>
+        <v>615560</v>
       </c>
       <c r="R10" t="n">
-        <v>6972912</v>
+        <v>6972753</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>396</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1780,10 +1780,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123299550</v>
+        <v>123299533</v>
       </c>
       <c r="B11" t="n">
-        <v>91402</v>
+        <v>90977</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1792,25 +1792,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1820,10 +1820,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>615477</v>
+        <v>615530</v>
       </c>
       <c r="R11" t="n">
-        <v>6972749</v>
+        <v>6972995</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>411</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Erik Lagerin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">

--- a/artfynd/A 38327-2024 artfynd.xlsx
+++ b/artfynd/A 38327-2024 artfynd.xlsx
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123299543</v>
+        <v>123299547</v>
       </c>
       <c r="B6" t="n">
-        <v>57481</v>
+        <v>90986</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>615509</v>
+        <v>615560</v>
       </c>
       <c r="R6" t="n">
-        <v>6972912</v>
+        <v>6972753</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>396</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123299534</v>
+        <v>123299550</v>
       </c>
       <c r="B7" t="n">
-        <v>90981</v>
+        <v>91411</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1308,25 +1308,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>615549</v>
+        <v>615477</v>
       </c>
       <c r="R7" t="n">
-        <v>6972986</v>
+        <v>6972749</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>393</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erik Lagerin</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123299550</v>
+        <v>123299543</v>
       </c>
       <c r="B8" t="n">
-        <v>91408</v>
+        <v>57481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>615477</v>
+        <v>615509</v>
       </c>
       <c r="R8" t="n">
-        <v>6972749</v>
+        <v>6972912</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>400</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Erik Lagerin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1538,10 +1538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123299521</v>
+        <v>123299534</v>
       </c>
       <c r="B9" t="n">
-        <v>79853</v>
+        <v>90984</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1554,21 +1554,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>615350</v>
+        <v>615549</v>
       </c>
       <c r="R9" t="n">
-        <v>6972780</v>
+        <v>6972986</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>410</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1659,10 +1659,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123299547</v>
+        <v>123299533</v>
       </c>
       <c r="B10" t="n">
-        <v>90983</v>
+        <v>90980</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1675,21 +1675,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>615560</v>
+        <v>615530</v>
       </c>
       <c r="R10" t="n">
-        <v>6972753</v>
+        <v>6972995</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>411</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1780,10 +1780,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123299533</v>
+        <v>123299521</v>
       </c>
       <c r="B11" t="n">
-        <v>90977</v>
+        <v>79856</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1796,21 +1796,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1820,10 +1820,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>615530</v>
+        <v>615350</v>
       </c>
       <c r="R11" t="n">
-        <v>6972995</v>
+        <v>6972780</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>423</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 38327-2024 artfynd.xlsx
+++ b/artfynd/A 38327-2024 artfynd.xlsx
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123299547</v>
+        <v>123299543</v>
       </c>
       <c r="B6" t="n">
-        <v>90986</v>
+        <v>57487</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>615560</v>
+        <v>615509</v>
       </c>
       <c r="R6" t="n">
-        <v>6972753</v>
+        <v>6972912</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>400</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123299550</v>
+        <v>123299547</v>
       </c>
       <c r="B7" t="n">
-        <v>91411</v>
+        <v>91003</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1308,25 +1308,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>615477</v>
+        <v>615560</v>
       </c>
       <c r="R7" t="n">
-        <v>6972749</v>
+        <v>6972753</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>396</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Erik Lagerin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123299543</v>
+        <v>123299521</v>
       </c>
       <c r="B8" t="n">
-        <v>57481</v>
+        <v>79862</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>615509</v>
+        <v>615350</v>
       </c>
       <c r="R8" t="n">
-        <v>6972912</v>
+        <v>6972780</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>423</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1541,7 +1541,7 @@
         <v>123299534</v>
       </c>
       <c r="B9" t="n">
-        <v>90984</v>
+        <v>91001</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1659,10 +1659,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123299533</v>
+        <v>123299550</v>
       </c>
       <c r="B10" t="n">
-        <v>90980</v>
+        <v>91428</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1671,25 +1671,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>615530</v>
+        <v>615477</v>
       </c>
       <c r="R10" t="n">
-        <v>6972995</v>
+        <v>6972749</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>393</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erik Lagerin</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1780,10 +1780,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123299521</v>
+        <v>123299533</v>
       </c>
       <c r="B11" t="n">
-        <v>79856</v>
+        <v>90997</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1796,21 +1796,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1820,10 +1820,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>615350</v>
+        <v>615530</v>
       </c>
       <c r="R11" t="n">
-        <v>6972780</v>
+        <v>6972995</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>411</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 38327-2024 artfynd.xlsx
+++ b/artfynd/A 38327-2024 artfynd.xlsx
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123299543</v>
+        <v>123299550</v>
       </c>
       <c r="B6" t="n">
-        <v>57487</v>
+        <v>91433</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1187,25 +1187,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>615509</v>
+        <v>615477</v>
       </c>
       <c r="R6" t="n">
-        <v>6972912</v>
+        <v>6972749</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>393</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erik Lagerin</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1296,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123299547</v>
+        <v>123299521</v>
       </c>
       <c r="B7" t="n">
-        <v>91003</v>
+        <v>79867</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,21 +1312,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>615560</v>
+        <v>615350</v>
       </c>
       <c r="R7" t="n">
-        <v>6972753</v>
+        <v>6972780</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>423</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123299521</v>
+        <v>123299533</v>
       </c>
       <c r="B8" t="n">
-        <v>79862</v>
+        <v>91002</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>615350</v>
+        <v>615530</v>
       </c>
       <c r="R8" t="n">
-        <v>6972780</v>
+        <v>6972995</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>411</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1541,7 +1541,7 @@
         <v>123299534</v>
       </c>
       <c r="B9" t="n">
-        <v>91001</v>
+        <v>91006</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1659,10 +1659,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123299550</v>
+        <v>123299543</v>
       </c>
       <c r="B10" t="n">
-        <v>91428</v>
+        <v>57490</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1671,25 +1671,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>615477</v>
+        <v>615509</v>
       </c>
       <c r="R10" t="n">
-        <v>6972749</v>
+        <v>6972912</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>400</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Erik Lagerin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1780,10 +1780,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123299533</v>
+        <v>123299547</v>
       </c>
       <c r="B11" t="n">
-        <v>90997</v>
+        <v>91008</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1796,21 +1796,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1820,10 +1820,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>615530</v>
+        <v>615560</v>
       </c>
       <c r="R11" t="n">
-        <v>6972995</v>
+        <v>6972753</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>396</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 38327-2024 artfynd.xlsx
+++ b/artfynd/A 38327-2024 artfynd.xlsx
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123299550</v>
+        <v>123299534</v>
       </c>
       <c r="B6" t="n">
-        <v>91433</v>
+        <v>91008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1187,25 +1187,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>615477</v>
+        <v>615549</v>
       </c>
       <c r="R6" t="n">
-        <v>6972749</v>
+        <v>6972986</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>410</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Erik Lagerin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1296,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123299521</v>
+        <v>123299533</v>
       </c>
       <c r="B7" t="n">
-        <v>79867</v>
+        <v>91004</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,21 +1312,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>615350</v>
+        <v>615530</v>
       </c>
       <c r="R7" t="n">
-        <v>6972780</v>
+        <v>6972995</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>411</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123299533</v>
+        <v>123299543</v>
       </c>
       <c r="B8" t="n">
-        <v>91002</v>
+        <v>57491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>615530</v>
+        <v>615509</v>
       </c>
       <c r="R8" t="n">
-        <v>6972995</v>
+        <v>6972912</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>400</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1538,10 +1538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123299534</v>
+        <v>123299547</v>
       </c>
       <c r="B9" t="n">
-        <v>91006</v>
+        <v>91010</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1554,21 +1554,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>615549</v>
+        <v>615560</v>
       </c>
       <c r="R9" t="n">
-        <v>6972986</v>
+        <v>6972753</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>396</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1659,10 +1659,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123299543</v>
+        <v>123299550</v>
       </c>
       <c r="B10" t="n">
-        <v>57490</v>
+        <v>91435</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1671,25 +1671,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>615509</v>
+        <v>615477</v>
       </c>
       <c r="R10" t="n">
-        <v>6972912</v>
+        <v>6972749</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>393</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erik Lagerin</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1780,10 +1780,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123299547</v>
+        <v>123299521</v>
       </c>
       <c r="B11" t="n">
-        <v>91008</v>
+        <v>79869</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1796,21 +1796,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1820,10 +1820,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>615560</v>
+        <v>615350</v>
       </c>
       <c r="R11" t="n">
-        <v>6972753</v>
+        <v>6972780</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>423</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 38327-2024 artfynd.xlsx
+++ b/artfynd/A 38327-2024 artfynd.xlsx
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123299534</v>
+        <v>123299543</v>
       </c>
       <c r="B6" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>615549</v>
+        <v>615509</v>
       </c>
       <c r="R6" t="n">
-        <v>6972986</v>
+        <v>6972912</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>400</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123299533</v>
+        <v>123299534</v>
       </c>
       <c r="B7" t="n">
-        <v>91004</v>
+        <v>91008</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,21 +1312,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>615530</v>
+        <v>615549</v>
       </c>
       <c r="R7" t="n">
-        <v>6972995</v>
+        <v>6972986</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>410</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123299543</v>
+        <v>123299533</v>
       </c>
       <c r="B8" t="n">
-        <v>57491</v>
+        <v>91004</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>615509</v>
+        <v>615530</v>
       </c>
       <c r="R8" t="n">
-        <v>6972912</v>
+        <v>6972995</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>411</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1538,10 +1538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123299547</v>
+        <v>123299521</v>
       </c>
       <c r="B9" t="n">
-        <v>91010</v>
+        <v>79869</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1554,21 +1554,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>615560</v>
+        <v>615350</v>
       </c>
       <c r="R9" t="n">
-        <v>6972753</v>
+        <v>6972780</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>423</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1659,10 +1659,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123299550</v>
+        <v>123299547</v>
       </c>
       <c r="B10" t="n">
-        <v>91435</v>
+        <v>91010</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1671,25 +1671,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>615477</v>
+        <v>615560</v>
       </c>
       <c r="R10" t="n">
-        <v>6972749</v>
+        <v>6972753</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>396</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Erik Lagerin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1780,10 +1780,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123299521</v>
+        <v>123299550</v>
       </c>
       <c r="B11" t="n">
-        <v>79869</v>
+        <v>91435</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1792,25 +1792,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1820,10 +1820,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>615350</v>
+        <v>615477</v>
       </c>
       <c r="R11" t="n">
-        <v>6972780</v>
+        <v>6972749</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>393</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erik Lagerin</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">

--- a/artfynd/A 38327-2024 artfynd.xlsx
+++ b/artfynd/A 38327-2024 artfynd.xlsx
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123299543</v>
+        <v>123299534</v>
       </c>
       <c r="B6" t="n">
-        <v>57491</v>
+        <v>91008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>615509</v>
+        <v>615549</v>
       </c>
       <c r="R6" t="n">
-        <v>6972912</v>
+        <v>6972986</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>410</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123299534</v>
+        <v>123299547</v>
       </c>
       <c r="B7" t="n">
-        <v>91008</v>
+        <v>91010</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,21 +1312,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>615549</v>
+        <v>615560</v>
       </c>
       <c r="R7" t="n">
-        <v>6972986</v>
+        <v>6972753</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>396</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123299533</v>
+        <v>123299521</v>
       </c>
       <c r="B8" t="n">
-        <v>91004</v>
+        <v>79869</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>615530</v>
+        <v>615350</v>
       </c>
       <c r="R8" t="n">
-        <v>6972995</v>
+        <v>6972780</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>423</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1538,10 +1538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123299521</v>
+        <v>123299543</v>
       </c>
       <c r="B9" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1554,21 +1554,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>615350</v>
+        <v>615509</v>
       </c>
       <c r="R9" t="n">
-        <v>6972780</v>
+        <v>6972912</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>400</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1659,10 +1659,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123299547</v>
+        <v>123299550</v>
       </c>
       <c r="B10" t="n">
-        <v>91010</v>
+        <v>91435</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1671,25 +1671,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>615560</v>
+        <v>615477</v>
       </c>
       <c r="R10" t="n">
-        <v>6972753</v>
+        <v>6972749</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>393</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erik Lagerin</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1780,10 +1780,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123299550</v>
+        <v>123299533</v>
       </c>
       <c r="B11" t="n">
-        <v>91435</v>
+        <v>91004</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1792,25 +1792,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1820,10 +1820,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>615477</v>
+        <v>615530</v>
       </c>
       <c r="R11" t="n">
-        <v>6972749</v>
+        <v>6972995</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>411</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Erik Lagerin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">

--- a/artfynd/A 38327-2024 artfynd.xlsx
+++ b/artfynd/A 38327-2024 artfynd.xlsx
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123299534</v>
+        <v>123299547</v>
       </c>
       <c r="B6" t="n">
-        <v>91008</v>
+        <v>91010</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>615549</v>
+        <v>615560</v>
       </c>
       <c r="R6" t="n">
-        <v>6972986</v>
+        <v>6972753</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>396</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123299547</v>
+        <v>123299533</v>
       </c>
       <c r="B7" t="n">
-        <v>91010</v>
+        <v>91004</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,21 +1312,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>615560</v>
+        <v>615530</v>
       </c>
       <c r="R7" t="n">
-        <v>6972753</v>
+        <v>6972995</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>411</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123299521</v>
+        <v>123299534</v>
       </c>
       <c r="B8" t="n">
-        <v>79869</v>
+        <v>91008</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>615350</v>
+        <v>615549</v>
       </c>
       <c r="R8" t="n">
-        <v>6972780</v>
+        <v>6972986</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>410</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1538,10 +1538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123299543</v>
+        <v>123299550</v>
       </c>
       <c r="B9" t="n">
-        <v>57491</v>
+        <v>91435</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1550,25 +1550,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>615509</v>
+        <v>615477</v>
       </c>
       <c r="R9" t="n">
-        <v>6972912</v>
+        <v>6972749</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>393</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erik Lagerin</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1659,10 +1659,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123299550</v>
+        <v>123299543</v>
       </c>
       <c r="B10" t="n">
-        <v>91435</v>
+        <v>57491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1671,25 +1671,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>615477</v>
+        <v>615509</v>
       </c>
       <c r="R10" t="n">
-        <v>6972749</v>
+        <v>6972912</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>400</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Erik Lagerin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1780,10 +1780,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123299533</v>
+        <v>123299521</v>
       </c>
       <c r="B11" t="n">
-        <v>91004</v>
+        <v>79869</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1796,21 +1796,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1820,10 +1820,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>615530</v>
+        <v>615350</v>
       </c>
       <c r="R11" t="n">
-        <v>6972995</v>
+        <v>6972780</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>423</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 38327-2024 artfynd.xlsx
+++ b/artfynd/A 38327-2024 artfynd.xlsx
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123299547</v>
+        <v>123299534</v>
       </c>
       <c r="B6" t="n">
-        <v>91010</v>
+        <v>91008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>615560</v>
+        <v>615549</v>
       </c>
       <c r="R6" t="n">
-        <v>6972753</v>
+        <v>6972986</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>410</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123299533</v>
+        <v>123299543</v>
       </c>
       <c r="B7" t="n">
-        <v>91004</v>
+        <v>57491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,21 +1312,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>615530</v>
+        <v>615509</v>
       </c>
       <c r="R7" t="n">
-        <v>6972995</v>
+        <v>6972912</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>400</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123299534</v>
+        <v>123299550</v>
       </c>
       <c r="B8" t="n">
-        <v>91008</v>
+        <v>91435</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>615549</v>
+        <v>615477</v>
       </c>
       <c r="R8" t="n">
-        <v>6972986</v>
+        <v>6972749</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>393</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erik Lagerin</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1538,10 +1538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123299550</v>
+        <v>123299533</v>
       </c>
       <c r="B9" t="n">
-        <v>91435</v>
+        <v>91004</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1550,25 +1550,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>615477</v>
+        <v>615530</v>
       </c>
       <c r="R9" t="n">
-        <v>6972749</v>
+        <v>6972995</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>411</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Erik Lagerin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1659,10 +1659,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123299543</v>
+        <v>123299521</v>
       </c>
       <c r="B10" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1675,21 +1675,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>615509</v>
+        <v>615350</v>
       </c>
       <c r="R10" t="n">
-        <v>6972912</v>
+        <v>6972780</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>423</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1780,10 +1780,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123299521</v>
+        <v>123299547</v>
       </c>
       <c r="B11" t="n">
-        <v>79869</v>
+        <v>91010</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1796,21 +1796,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1820,10 +1820,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>615350</v>
+        <v>615560</v>
       </c>
       <c r="R11" t="n">
-        <v>6972780</v>
+        <v>6972753</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>396</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
